--- a/workspace/framework_paper/fp/gradient_fp_eval_schedulables.xlsx
+++ b/workspace/framework_paper/fp/gradient_fp_eval_schedulables.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,16 +442,6 @@
           <t>bf</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>eqs</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>eqf</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -472,12 +462,6 @@
       <c r="F2" t="n">
         <v>50</v>
       </c>
-      <c r="G2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H2" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -498,12 +482,6 @@
       <c r="F3" t="n">
         <v>50</v>
       </c>
-      <c r="G3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H3" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -524,12 +502,6 @@
       <c r="F4" t="n">
         <v>50</v>
       </c>
-      <c r="G4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -550,12 +522,6 @@
       <c r="F5" t="n">
         <v>50</v>
       </c>
-      <c r="G5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H5" t="n">
-        <v>49</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -576,12 +542,6 @@
       <c r="F6" t="n">
         <v>50</v>
       </c>
-      <c r="G6" t="n">
-        <v>50</v>
-      </c>
-      <c r="H6" t="n">
-        <v>49</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -602,12 +562,6 @@
       <c r="F7" t="n">
         <v>50</v>
       </c>
-      <c r="G7" t="n">
-        <v>50</v>
-      </c>
-      <c r="H7" t="n">
-        <v>49</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -628,37 +582,25 @@
       <c r="F8" t="n">
         <v>50</v>
       </c>
-      <c r="G8" t="n">
-        <v>49</v>
-      </c>
-      <c r="H8" t="n">
-        <v>48</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
-      </c>
-      <c r="G9" t="n">
-        <v>47</v>
-      </c>
-      <c r="H9" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -666,25 +608,19 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G10" t="n">
-        <v>46</v>
-      </c>
-      <c r="H10" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -692,25 +628,19 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
-      </c>
-      <c r="G11" t="n">
-        <v>46</v>
-      </c>
-      <c r="H11" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -718,25 +648,19 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
-      </c>
-      <c r="G12" t="n">
-        <v>41</v>
-      </c>
-      <c r="H12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -744,25 +668,19 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
-      </c>
-      <c r="G13" t="n">
-        <v>38</v>
-      </c>
-      <c r="H13" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -770,25 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
-      </c>
-      <c r="G14" t="n">
-        <v>38</v>
-      </c>
-      <c r="H14" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -796,25 +708,19 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
-      </c>
-      <c r="G15" t="n">
-        <v>32</v>
-      </c>
-      <c r="H15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -822,25 +728,19 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
-      </c>
-      <c r="G16" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -848,25 +748,19 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
-      </c>
-      <c r="G17" t="n">
-        <v>29</v>
-      </c>
-      <c r="H17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -874,25 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
-      </c>
-      <c r="G18" t="n">
-        <v>25</v>
-      </c>
-      <c r="H18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -900,25 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
-      </c>
-      <c r="G19" t="n">
-        <v>19</v>
-      </c>
-      <c r="H19" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -926,25 +808,19 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>28</v>
-      </c>
-      <c r="G20" t="n">
-        <v>16</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -952,25 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10</v>
-      </c>
-      <c r="H21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/fp/gradient_fp_eval_schedulables.xlsx
+++ b/workspace/framework_paper/fp/gradient_fp_eval_schedulables.xlsx
@@ -588,19 +588,19 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -608,19 +608,19 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -628,19 +628,19 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -648,19 +648,19 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -668,19 +668,19 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -688,19 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -708,19 +708,19 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -728,19 +728,19 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
@@ -748,19 +748,19 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
@@ -768,19 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -788,19 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -808,19 +808,19 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -828,19 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
